--- a/01_INPUTS/04D_MAESTRO_PRODUCTOS_PENAFLOR.xlsx
+++ b/01_INPUTS/04D_MAESTRO_PRODUCTOS_PENAFLOR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -9676,6 +9676,42 @@
         <v>24</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Antares</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Cerveza Lager</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>60022</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ANTARES LAGER 660 6X660 (60022)</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H260" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/01_INPUTS/04D_MAESTRO_PRODUCTOS_PENAFLOR.xlsx
+++ b/01_INPUTS/04D_MAESTRO_PRODUCTOS_PENAFLOR.xlsx
@@ -413,10 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A2:H263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
@@ -9709,6 +9708,114 @@
         <v>3.96</v>
       </c>
       <c r="H260" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Antares</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Antares Clasicas</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>30329</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ANTARES LATA KOLSCH 6 X 473ML</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="H261" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Antares</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Antares Clasicas</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>30343</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>ANTARES LATA SCOTCH 6 X 473ML</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="H262" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Antares</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Antares Especiales</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>30268</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Cerveza Artesanal</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>ANTARES LATA CARAVANA 6 X 473ML</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="H263" t="n">
         <v>6</v>
       </c>
     </row>
